--- a/组合介绍/report_assets/main/workbooks/4-Microsoft_Excel_Worksheet4.xlsx
+++ b/组合介绍/report_assets/main/workbooks/4-Microsoft_Excel_Worksheet4.xlsx
@@ -68,7 +68,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -76,6 +75,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -137,10 +137,10 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="164" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" applyProtection="false" borderId="3" fillId="0" fontId="2" numFmtId="164" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -464,42 +464,42 @@
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" s="3" t="str">
         <v>资产类别</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" s="3" t="str">
         <v>相对总利润贡献占比</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="1" t="str">
         <v>股票端</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>0.416</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="1" t="str">
         <v>商品端</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>0.269</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="str">
+      <c r="A4" s="1" t="str">
         <v>可转债</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>0.24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="str">
+      <c r="A5" s="1" t="str">
         <v>纯债基</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>0.075</v>
       </c>
     </row>
